--- a/Assets/Data/DataTable/02_Skill_Table.xlsx
+++ b/Assets/Data/DataTable/02_Skill_Table.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28928"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdw33\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D260E7-370C-40EE-BE34-C2C22A81C950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FEC2A4-F77F-4C01-90F5-B14910B6CFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B5397950-1C80-4B01-B947-A4015F39B3CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B5397950-1C80-4B01-B947-A4015F39B3CD}"/>
   </bookViews>
   <sheets>
     <sheet name="!Logic" sheetId="2" r:id="rId1"/>
     <sheet name="!Skill_Rule" sheetId="3" r:id="rId2"/>
     <sheet name="Skill_Table" sheetId="1" r:id="rId3"/>
+    <sheet name="Skill_Table_fix" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,8 +38,64 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={777EDFB7-0CD9-49CF-A5E1-449267D67B1E}</author>
+    <author>tc={45253023-AE41-49E1-8108-320D3E54524D}</author>
+    <author>tc={D873E6BB-D74F-4BBF-9484-8FDF8853F5F3}</author>
+    <author>tc={851349FB-1E22-4FBB-81E6-6E0ADE8AA0B8}</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{777EDFB7-0CD9-49CF-A5E1-449267D67B1E}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    0: None
+1: Passive
+2: Attack
+3: Heal
+4: Support</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="1" shapeId="0" xr:uid="{45253023-AE41-49E1-8108-320D3E54524D}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    0: None
+1: Player
+2: Enemy</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="2" shapeId="0" xr:uid="{D873E6BB-D74F-4BBF-9484-8FDF8853F5F3}">
+      <text>
+        <t>[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    0: None
+1: Single
+2: All
+3: Random
+4: Splash</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="3" shapeId="0" xr:uid="{851349FB-1E22-4FBB-81E6-6E0ADE8AA0B8}">
+      <text>
+        <t xml:space="preserve">[스레드 댓글]
+사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
+댓글:
+    크게 증가, 작게 증가, 그냥 증가
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="196">
   <si>
     <t>칼럼명</t>
   </si>
@@ -653,6 +710,74 @@
   </si>
   <si>
     <t>Skill_EFFECT_DESCE_3010</t>
+  </si>
+  <si>
+    <t>스킬 타입</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACTION_TARGET_TYPE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 적용 대상 타입</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 적용 범위 타입</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Type</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Side</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Effect_Duration_Turns</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 지속 턴</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 계수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>적용 횟수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 속성 게이지 계수</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Element_Rate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:SKILL_TYPE:NONE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:ACTION_TARGET_TYPE:NONE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:SIDE:NONE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum:SKILL_ELEMENT_RATE:NONE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>버프 디버프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -662,7 +787,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,6 +871,12 @@
       <name val="AppleSDGothicNeoEB00"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1205,6 +1336,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="동우 제" id="{2F92C769-78D7-4307-AC17-B3141EBFEAE2}" userId="b4acf424e0b596a4" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1522,10 +1659,39 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D3" dT="2025-10-21T07:27:58.84" personId="{2F92C769-78D7-4307-AC17-B3141EBFEAE2}" id="{777EDFB7-0CD9-49CF-A5E1-449267D67B1E}">
+    <text>0: None
+1: Passive
+2: Attack
+3: Heal
+4: Support</text>
+  </threadedComment>
+  <threadedComment ref="E3" dT="2025-10-21T07:29:53.20" personId="{2F92C769-78D7-4307-AC17-B3141EBFEAE2}" id="{45253023-AE41-49E1-8108-320D3E54524D}">
+    <text>0: None
+1: Player
+2: Enemy</text>
+  </threadedComment>
+  <threadedComment ref="F3" dT="2025-10-21T07:25:32.12" personId="{2F92C769-78D7-4307-AC17-B3141EBFEAE2}" id="{D873E6BB-D74F-4BBF-9484-8FDF8853F5F3}">
+    <text>0: None
+1: Single
+2: All
+3: Random
+4: Splash</text>
+  </threadedComment>
+  <threadedComment ref="K3" dT="2025-10-21T09:11:24.52" personId="{2F92C769-78D7-4307-AC17-B3141EBFEAE2}" id="{851349FB-1E22-4FBB-81E6-6E0ADE8AA0B8}">
+    <text xml:space="preserve">크게 증가, 작게 증가, 그냥 증가
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA9A9631-B89D-4555-BF41-645689E096BC}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.75" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
@@ -1543,7 +1709,7 @@
     <col min="18" max="18" width="74.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27" customHeight="1">
+    <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
@@ -1566,7 +1732,7 @@
       <c r="I1" s="52"/>
       <c r="J1" s="53"/>
     </row>
-    <row r="2" spans="1:10" ht="50.25" customHeight="1">
+    <row r="2" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="40" t="s">
         <v>6</v>
       </c>
@@ -1593,7 +1759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="50.25" customHeight="1">
+    <row r="3" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="40" t="s">
         <v>13</v>
       </c>
@@ -1620,7 +1786,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="50.25" customHeight="1">
+    <row r="4" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="40" t="s">
         <v>19</v>
       </c>
@@ -1647,7 +1813,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="50.25" customHeight="1">
+    <row r="5" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="s">
         <v>26</v>
       </c>
@@ -1674,7 +1840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="50.25" customHeight="1">
+    <row r="6" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="40" t="s">
         <v>32</v>
       </c>
@@ -1701,7 +1867,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="50.25" customHeight="1">
+    <row r="7" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="40" t="s">
         <v>39</v>
       </c>
@@ -1728,7 +1894,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="50.25" customHeight="1">
+    <row r="8" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="40" t="s">
         <v>46</v>
       </c>
@@ -1743,7 +1909,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="50.25" customHeight="1">
+    <row r="9" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="40" t="s">
         <v>49</v>
       </c>
@@ -1758,7 +1924,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="50.25" customHeight="1">
+    <row r="10" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>53</v>
       </c>
@@ -1779,7 +1945,7 @@
       <c r="I10" s="50"/>
       <c r="J10" s="51"/>
     </row>
-    <row r="11" spans="1:10" ht="50.25" customHeight="1">
+    <row r="11" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="40" t="s">
         <v>57</v>
       </c>
@@ -1806,7 +1972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="33">
+    <row r="12" spans="1:10" ht="33" x14ac:dyDescent="0.3">
       <c r="A12" s="40" t="s">
         <v>60</v>
       </c>
@@ -1833,7 +1999,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="66">
+    <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A13" s="40" t="s">
         <v>65</v>
       </c>
@@ -1860,7 +2026,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="82.5" customHeight="1">
+    <row r="14" spans="1:10" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="40" t="s">
         <v>71</v>
       </c>
@@ -1887,7 +2053,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="99" customHeight="1">
+    <row r="15" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="40" t="s">
         <v>77</v>
       </c>
@@ -1914,11 +2080,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="16:18" ht="97.5" customHeight="1"/>
-    <row r="29" spans="16:18" ht="97.5" customHeight="1"/>
-    <row r="30" spans="16:18" ht="97.5" customHeight="1"/>
-    <row r="31" spans="16:18" ht="97.5" customHeight="1"/>
-    <row r="32" spans="16:18">
+    <row r="28" spans="16:18" ht="97.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="16:18" ht="97.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="16:18" ht="97.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="16:18" ht="97.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="16:18" x14ac:dyDescent="0.3">
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
@@ -1935,8 +2101,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15E9AD6-621B-4423-8E21-B768BF6DE728}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="18.875" customWidth="1"/>
     <col min="4" max="7" width="17.75" customWidth="1"/>
@@ -1945,7 +2112,7 @@
     <col min="13" max="13" width="108" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
         <v>83</v>
       </c>
@@ -1962,7 +2129,7 @@
       <c r="L1" s="54"/>
       <c r="M1" s="54"/>
     </row>
-    <row r="2" spans="1:13" ht="47.25" customHeight="1">
+    <row r="2" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="55"/>
       <c r="B2" s="55"/>
       <c r="C2" s="55"/>
@@ -1977,7 +2144,7 @@
       <c r="L2" s="55"/>
       <c r="M2" s="55"/>
     </row>
-    <row r="3" spans="1:13" ht="47.25" customHeight="1">
+    <row r="3" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>84</v>
       </c>
@@ -2018,7 +2185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="47.25" customHeight="1">
+    <row r="4" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>95</v>
       </c>
@@ -2049,7 +2216,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="47.25" customHeight="1">
+    <row r="5" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>95</v>
       </c>
@@ -2080,7 +2247,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="47.25" customHeight="1">
+    <row r="6" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>103</v>
       </c>
@@ -2111,7 +2278,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="47.25" customHeight="1">
+    <row r="7" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>103</v>
       </c>
@@ -2142,7 +2309,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="47.25" customHeight="1">
+    <row r="8" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>108</v>
       </c>
@@ -2173,7 +2340,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="47.25" customHeight="1">
+    <row r="9" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>108</v>
       </c>
@@ -2214,7 +2381,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="47.25" customHeight="1">
+    <row r="10" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>115</v>
       </c>
@@ -2253,7 +2420,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="47.25" customHeight="1">
+    <row r="11" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>115</v>
       </c>
@@ -2294,7 +2461,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="63" customHeight="1">
+    <row r="12" spans="1:13" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>122</v>
       </c>
@@ -2325,7 +2492,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="63" customHeight="1">
+    <row r="13" spans="1:13" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>122</v>
       </c>
@@ -2377,8 +2544,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CBDFF2-7524-4AD5-B513-A4E52FA90550}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
     <col min="2" max="2" width="23.625" customWidth="1"/>
@@ -2396,7 +2564,7 @@
     <col min="14" max="15" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>128</v>
       </c>
@@ -2415,7 +2583,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="30"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
         <v>129</v>
       </c>
@@ -2459,7 +2627,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="31" t="s">
         <v>143</v>
       </c>
@@ -2503,7 +2671,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>148</v>
       </c>
@@ -2547,7 +2715,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>20010001</v>
       </c>
@@ -2581,7 +2749,7 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>20010002</v>
       </c>
@@ -2615,7 +2783,7 @@
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>20020001</v>
       </c>
@@ -2649,7 +2817,7 @@
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>20020002</v>
       </c>
@@ -2683,7 +2851,7 @@
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>20030001</v>
       </c>
@@ -2717,7 +2885,7 @@
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>20030002</v>
       </c>
@@ -2761,7 +2929,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>20040001</v>
       </c>
@@ -2803,7 +2971,7 @@
       </c>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>20040002</v>
       </c>
@@ -2847,7 +3015,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>20050001</v>
       </c>
@@ -2881,7 +3049,7 @@
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>20050002</v>
       </c>
@@ -2929,4 +3097,455 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C2397E-2B9D-475C-8AD1-7262A65C07C1}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="23.625" customWidth="1"/>
+    <col min="3" max="3" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="24.25" customWidth="1"/>
+    <col min="6" max="6" width="34" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.125" customWidth="1"/>
+    <col min="8" max="8" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.25" customWidth="1"/>
+    <col min="11" max="11" width="36.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="13" max="13" width="28.75" customWidth="1"/>
+    <col min="14" max="14" width="16.125" customWidth="1"/>
+    <col min="15" max="15" width="23" customWidth="1"/>
+    <col min="16" max="16" width="32.375" customWidth="1"/>
+    <col min="17" max="18" width="16.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="30"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="J2" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="K2" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="32"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>20010001</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>20010002</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>20020001</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>20020002</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>20030001</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8">
+        <v>3</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>20030002</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="6"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>20040001</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="6"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>20040002</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="6">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="6"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>20050001</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="6">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>20050002</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8">
+        <v>2</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>